--- a/指标.xlsx
+++ b/指标.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>客户简称</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>DA中环百联</t>
+  </si>
+  <si>
+    <t>TX长沙</t>
   </si>
 </sst>
 </file>
@@ -112,7 +115,7 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,6 +149,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -292,7 +301,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -319,6 +328,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -504,7 +519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -609,6 +624,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -725,55 +755,52 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -788,74 +815,77 @@
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -894,6 +924,9 @@
     </xf>
     <xf numFmtId="176" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1420,7 +1453,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818" style="1" customWidth="1"/>
@@ -1894,6 +1927,32 @@
         <v>50000</v>
       </c>
     </row>
+    <row r="13" ht="14.5" spans="1:13">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H13" s="13">
+        <v>190000</v>
+      </c>
+      <c r="I13" s="13">
+        <v>215000</v>
+      </c>
+      <c r="J13" s="13">
+        <v>220000</v>
+      </c>
+      <c r="K13" s="13">
+        <v>250000</v>
+      </c>
+      <c r="L13" s="13">
+        <v>210000</v>
+      </c>
+      <c r="M13" s="13">
+        <v>235000</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/指标.xlsx
+++ b/指标.xlsx
@@ -1901,19 +1901,19 @@
         <v>84000</v>
       </c>
       <c r="I11" s="1">
+        <v>72000</v>
+      </c>
+      <c r="J11" s="1">
         <v>84000</v>
       </c>
-      <c r="J11" s="1">
-        <v>96000</v>
-      </c>
       <c r="K11" s="1">
-        <v>120000</v>
+        <v>108000</v>
       </c>
       <c r="L11" s="1">
-        <v>100000</v>
+        <v>88000</v>
       </c>
       <c r="M11" s="1">
-        <v>120000</v>
+        <v>108000</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1925,6 +1925,24 @@
       </c>
       <c r="G12" s="1">
         <v>50000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>60000</v>
+      </c>
+      <c r="I12" s="1">
+        <v>60000</v>
+      </c>
+      <c r="J12" s="1">
+        <v>60000</v>
+      </c>
+      <c r="K12" s="1">
+        <v>70000</v>
+      </c>
+      <c r="L12" s="1">
+        <v>60000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>70000</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:13">

--- a/指标.xlsx
+++ b/指标.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>客户简称</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>TX长沙</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -1453,7 +1456,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818" style="1" customWidth="1"/>
@@ -1971,8 +1974,14 @@
         <v>235000</v>
       </c>
     </row>
+    <row r="18" spans="6:6">
+      <c r="F18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/指标.xlsx
+++ b/指标.xlsx
@@ -27,45 +27,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>客户简称</t>
-  </si>
-  <si>
-    <t>1月</t>
-  </si>
-  <si>
-    <t>2月</t>
-  </si>
-  <si>
-    <t>3月</t>
-  </si>
-  <si>
-    <t>4月</t>
-  </si>
-  <si>
-    <t>5月</t>
-  </si>
-  <si>
-    <t>6月</t>
-  </si>
-  <si>
-    <t>7月</t>
-  </si>
-  <si>
-    <t>8月</t>
-  </si>
-  <si>
-    <t>9月</t>
-  </si>
-  <si>
-    <t>10月</t>
-  </si>
-  <si>
-    <t>11月</t>
-  </si>
-  <si>
-    <t>12月</t>
   </si>
   <si>
     <t>京东</t>
@@ -522,7 +486,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -537,19 +501,6 @@
       <right style="thin">
         <color theme="0" tint="-0.349986266670736"/>
       </right>
-      <top style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.349986266670736"/>
-      </left>
-      <right/>
       <top style="thin">
         <color theme="0" tint="-0.349986266670736"/>
       </top>
@@ -764,7 +715,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -776,34 +727,34 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -888,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -898,37 +849,34 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="5" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1460,11 +1408,10 @@
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.8181818181818" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.72727272727273" style="1"/>
-    <col min="3" max="3" width="8.72727272727273" style="1"/>
-    <col min="4" max="4" width="9.72727272727273" style="1"/>
+    <col min="2" max="4" width="9.72727272727273" style="1"/>
     <col min="5" max="5" width="9.72727272727273" style="1" customWidth="1"/>
-    <col min="6" max="13" width="9.72727272727273" style="1"/>
+    <col min="6" max="10" width="9.72727272727273" style="1"/>
+    <col min="11" max="13" width="10.7272727272727" style="1"/>
     <col min="14" max="16384" width="8.72727272727273" style="1"/>
   </cols>
   <sheetData>
@@ -1472,415 +1419,415 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>12</v>
+      <c r="B1" s="3">
+        <v>46023</v>
+      </c>
+      <c r="C1" s="3">
+        <v>46054</v>
+      </c>
+      <c r="D1" s="3">
+        <v>46082</v>
+      </c>
+      <c r="E1" s="3">
+        <v>46113</v>
+      </c>
+      <c r="F1" s="3">
+        <v>46143</v>
+      </c>
+      <c r="G1" s="3">
+        <v>46174</v>
+      </c>
+      <c r="H1" s="3">
+        <v>46204</v>
+      </c>
+      <c r="I1" s="3">
+        <v>46235</v>
+      </c>
+      <c r="J1" s="3">
+        <v>46266</v>
+      </c>
+      <c r="K1" s="3">
+        <v>46296</v>
+      </c>
+      <c r="L1" s="3">
+        <v>46327</v>
+      </c>
+      <c r="M1" s="3">
+        <v>46357</v>
       </c>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="6">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
         <v>91320</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="5">
         <v>96200</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="5">
         <v>120480</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>113680</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>173080</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>185520</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>126200</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>134600</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="5">
         <v>158800</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>303320</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>371800</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="6">
         <v>305000</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="6">
+      <c r="A3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
         <v>1428000</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <v>960000</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <v>1330000</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>1035000</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>1800000</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="5">
         <v>1545000</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>1166000</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>1386000</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="5">
         <v>1350000</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>3000000</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>2884000</v>
       </c>
-      <c r="M3" s="7">
+      <c r="M3" s="6">
         <v>2116000</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" s="6">
+      <c r="A4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
         <v>173740</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <v>130900</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <v>171360</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>123760</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>207060</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="5">
         <v>185640</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>130900</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>154700</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="5">
         <v>166600</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>292740</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="5">
         <v>345100</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="6">
         <v>297500</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="6">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
         <v>846800</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <v>638000</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>835200</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>603200</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>1009200</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>904800</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>638000</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>754000</v>
       </c>
-      <c r="J5" s="6">
+      <c r="J5" s="5">
         <v>812000</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>1426800</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>1682000</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="6">
         <v>1450000</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="6">
+      <c r="A6" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
         <v>31000</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>22400</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>46500</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>45000</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>62000</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>75000</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>77500</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>77500</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>75000</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>108500</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>120000</v>
       </c>
-      <c r="M6" s="7">
+      <c r="M6" s="6">
         <v>99600</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="10">
+      <c r="A7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9">
         <v>160000</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <v>120000</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="9">
         <v>140000</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>120000</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="9">
         <v>150000</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="9">
         <v>140000</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="9">
         <v>170000</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="9">
         <v>180000</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="9">
         <v>180000</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="9">
         <v>250000</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="9">
         <v>180000</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="10">
         <v>200000</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="6">
+      <c r="A8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
         <v>230000</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <v>200000</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>200000</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>180000</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>265000</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>240000</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>220000</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>255000</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>260000</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>280000</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>270000</v>
       </c>
-      <c r="M8" s="7">
+      <c r="M8" s="6">
         <v>280000</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="6">
+      <c r="A9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
         <v>195000</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <v>170000</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>190000</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>170000</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="11">
         <v>184000</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>210000</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>215000</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>240000</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>240000</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>280000</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>245000</v>
       </c>
-      <c r="M9" s="7">
+      <c r="M9" s="6">
         <v>255000</v>
       </c>
     </row>
     <row r="10" spans="1:13">
-      <c r="A10" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="6">
+      <c r="A10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
         <v>160000</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>120000</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>148000</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>145000</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>147000</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>190000</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>190000</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>215000</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>215000</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>250000</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>220000</v>
       </c>
-      <c r="M10" s="7">
+      <c r="M10" s="6">
         <v>235000</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1">
         <v>100000</v>
@@ -1921,7 +1868,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F12" s="1">
         <v>50000</v>
@@ -1950,33 +1897,33 @@
     </row>
     <row r="13" ht="14.5" spans="1:13">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G13" s="1">
         <v>5000</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="12">
         <v>190000</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="12">
         <v>215000</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="12">
         <v>220000</v>
       </c>
-      <c r="K13" s="13">
+      <c r="K13" s="12">
         <v>250000</v>
       </c>
-      <c r="L13" s="13">
+      <c r="L13" s="12">
         <v>210000</v>
       </c>
-      <c r="M13" s="13">
+      <c r="M13" s="12">
         <v>235000</v>
       </c>
     </row>
     <row r="18" spans="6:6">
       <c r="F18" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/指标.xlsx
+++ b/指标.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$M$13</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1410,7 +1413,9 @@
     <col min="1" max="1" width="11.8181818181818" style="1" customWidth="1"/>
     <col min="2" max="4" width="9.72727272727273" style="1"/>
     <col min="5" max="5" width="9.72727272727273" style="1" customWidth="1"/>
-    <col min="6" max="10" width="9.72727272727273" style="1"/>
+    <col min="6" max="6" width="9.72727272727273" style="1"/>
+    <col min="7" max="7" width="11.3636363636364" style="1" customWidth="1"/>
+    <col min="8" max="10" width="9.72727272727273" style="1"/>
     <col min="11" max="13" width="10.7272727272727" style="1"/>
     <col min="14" max="16384" width="8.72727272727273" style="1"/>
   </cols>
@@ -1763,25 +1768,25 @@
         <v>184000</v>
       </c>
       <c r="G9" s="5">
-        <v>210000</v>
+        <v>168000</v>
       </c>
       <c r="H9" s="5">
-        <v>215000</v>
+        <v>172000</v>
       </c>
       <c r="I9" s="5">
-        <v>240000</v>
+        <v>192000</v>
       </c>
       <c r="J9" s="5">
-        <v>240000</v>
+        <v>192000</v>
       </c>
       <c r="K9" s="5">
-        <v>280000</v>
+        <v>224000</v>
       </c>
       <c r="L9" s="5">
-        <v>245000</v>
+        <v>196000</v>
       </c>
       <c r="M9" s="6">
-        <v>255000</v>
+        <v>204000</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1804,25 +1809,25 @@
         <v>147000</v>
       </c>
       <c r="G10" s="5">
-        <v>190000</v>
+        <v>133000</v>
       </c>
       <c r="H10" s="5">
-        <v>190000</v>
+        <v>133000</v>
       </c>
       <c r="I10" s="5">
-        <v>215000</v>
+        <v>150500</v>
       </c>
       <c r="J10" s="5">
-        <v>215000</v>
+        <v>150500</v>
       </c>
       <c r="K10" s="5">
-        <v>250000</v>
+        <v>175000</v>
       </c>
       <c r="L10" s="5">
-        <v>220000</v>
+        <v>154000</v>
       </c>
       <c r="M10" s="6">
-        <v>235000</v>
+        <v>164500</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -1848,22 +1853,22 @@
         <v>96000</v>
       </c>
       <c r="H11" s="1">
+        <v>58800</v>
+      </c>
+      <c r="I11" s="1">
+        <v>58800</v>
+      </c>
+      <c r="J11" s="1">
+        <v>67200</v>
+      </c>
+      <c r="K11" s="1">
         <v>84000</v>
       </c>
-      <c r="I11" s="1">
-        <v>72000</v>
-      </c>
-      <c r="J11" s="1">
+      <c r="L11" s="1">
+        <v>70000</v>
+      </c>
+      <c r="M11" s="1">
         <v>84000</v>
-      </c>
-      <c r="K11" s="1">
-        <v>108000</v>
-      </c>
-      <c r="L11" s="1">
-        <v>88000</v>
-      </c>
-      <c r="M11" s="1">
-        <v>108000</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -1877,22 +1882,22 @@
         <v>50000</v>
       </c>
       <c r="H12" s="1">
-        <v>60000</v>
+        <v>42000</v>
       </c>
       <c r="I12" s="1">
-        <v>60000</v>
+        <v>42000</v>
       </c>
       <c r="J12" s="1">
-        <v>60000</v>
+        <v>42000</v>
       </c>
       <c r="K12" s="1">
-        <v>70000</v>
+        <v>49000</v>
       </c>
       <c r="L12" s="1">
-        <v>60000</v>
+        <v>42000</v>
       </c>
       <c r="M12" s="1">
-        <v>70000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="13" ht="14.5" spans="1:13">
@@ -1927,6 +1932,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:M13" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
